--- a/code/data/combined/pelg+jmul-w0wacdm-fixed.xlsx
+++ b/code/data/combined/pelg+jmul-w0wacdm-fixed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -480,25 +480,25 @@
         <v>543831.9299775055</v>
       </c>
       <c r="C2" t="n">
-        <v>-985857.647127157</v>
+        <v>-985857.6471271566</v>
       </c>
       <c r="D2" t="n">
-        <v>74888.07319703954</v>
+        <v>74888.07319703928</v>
       </c>
       <c r="E2" t="n">
         <v>221829.0705370776</v>
       </c>
       <c r="F2" t="n">
-        <v>-10062.16793669857</v>
+        <v>-10062.16793669851</v>
       </c>
       <c r="G2" t="n">
         <v>-22067.40475039123</v>
       </c>
       <c r="H2" t="n">
-        <v>-19574.61342722416</v>
+        <v>-19574.61342722418</v>
       </c>
       <c r="I2" t="n">
-        <v>-1859.913505855303</v>
+        <v>-1859.913505855309</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-985857.6471271084</v>
+        <v>-985857.6471271083</v>
       </c>
       <c r="C3" t="n">
-        <v>2505464.025069003</v>
+        <v>2505464.025069002</v>
       </c>
       <c r="D3" t="n">
-        <v>-410464.0118388796</v>
+        <v>-410464.0118388788</v>
       </c>
       <c r="E3" t="n">
-        <v>-423082.6601526615</v>
+        <v>-423082.6601526614</v>
       </c>
       <c r="F3" t="n">
-        <v>44839.0195306275</v>
+        <v>44839.01953062727</v>
       </c>
       <c r="G3" t="n">
-        <v>42500.38954621227</v>
+        <v>42500.38954621226</v>
       </c>
       <c r="H3" t="n">
-        <v>10982.3763259595</v>
+        <v>10982.37632595955</v>
       </c>
       <c r="I3" t="n">
-        <v>137.4427839614854</v>
+        <v>137.442783961505</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74888.07319701137</v>
+        <v>74888.07319701099</v>
       </c>
       <c r="C4" t="n">
-        <v>-410464.0118388071</v>
+        <v>-410464.0118388061</v>
       </c>
       <c r="D4" t="n">
-        <v>285152.2969908945</v>
+        <v>285152.2969908937</v>
       </c>
       <c r="E4" t="n">
-        <v>48556.94444977555</v>
+        <v>48556.94444977545</v>
       </c>
       <c r="F4" t="n">
-        <v>-98803.12100748756</v>
+        <v>-98803.12100748724</v>
       </c>
       <c r="G4" t="n">
-        <v>-5392.025980880036</v>
+        <v>-5392.025980880018</v>
       </c>
       <c r="H4" t="n">
-        <v>16151.80961625346</v>
+        <v>16151.80961625344</v>
       </c>
       <c r="I4" t="n">
-        <v>5443.11718748004</v>
+        <v>5443.117187480022</v>
       </c>
     </row>
     <row r="5">
@@ -573,10 +573,10 @@
         <v>221829.0705370767</v>
       </c>
       <c r="C5" t="n">
-        <v>-423082.6601526733</v>
+        <v>-423082.6601526732</v>
       </c>
       <c r="D5" t="n">
-        <v>48556.94444978445</v>
+        <v>48556.9444497844</v>
       </c>
       <c r="E5" t="n">
         <v>103838.2184716434</v>
@@ -588,10 +588,10 @@
         <v>-10113.71201078549</v>
       </c>
       <c r="H5" t="n">
-        <v>-7218.068523305056</v>
+        <v>-7218.06852330506</v>
       </c>
       <c r="I5" t="n">
-        <v>-727.9858571017814</v>
+        <v>-727.9858571017826</v>
       </c>
     </row>
     <row r="6">
@@ -601,28 +601,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-10062.16793665164</v>
+        <v>-10062.16793665151</v>
       </c>
       <c r="C6" t="n">
-        <v>44839.01953053412</v>
+        <v>44839.01953053374</v>
       </c>
       <c r="D6" t="n">
-        <v>-98803.1210074821</v>
+        <v>-98803.12100748187</v>
       </c>
       <c r="E6" t="n">
-        <v>-17728.69561108805</v>
+        <v>-17728.695611088</v>
       </c>
       <c r="F6" t="n">
-        <v>82575.26717293022</v>
+        <v>82575.26717293014</v>
       </c>
       <c r="G6" t="n">
-        <v>3933.386347637243</v>
+        <v>3933.386347637236</v>
       </c>
       <c r="H6" t="n">
-        <v>-1790.426177906254</v>
+        <v>-1790.426177906249</v>
       </c>
       <c r="I6" t="n">
-        <v>-1869.84114727765</v>
+        <v>-1869.841147277645</v>
       </c>
     </row>
     <row r="7">
@@ -635,25 +635,25 @@
         <v>-22067.40475038674</v>
       </c>
       <c r="C7" t="n">
-        <v>42500.38954620565</v>
+        <v>42500.38954620564</v>
       </c>
       <c r="D7" t="n">
-        <v>-5392.025980880551</v>
+        <v>-5392.025980880549</v>
       </c>
       <c r="E7" t="n">
         <v>-10113.71201078352</v>
       </c>
       <c r="F7" t="n">
-        <v>3933.386347639077</v>
+        <v>3933.386347639078</v>
       </c>
       <c r="G7" t="n">
         <v>1160.792167775459</v>
       </c>
       <c r="H7" t="n">
-        <v>923.7065237639254</v>
+        <v>923.7065237639257</v>
       </c>
       <c r="I7" t="n">
-        <v>84.40059098109444</v>
+        <v>84.40059098109448</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-19574.61342722518</v>
+        <v>-19574.61342722517</v>
       </c>
       <c r="C8" t="n">
-        <v>10982.3763259668</v>
+        <v>10982.37632596679</v>
       </c>
       <c r="D8" t="n">
-        <v>16151.8096162509</v>
+        <v>16151.80961625091</v>
       </c>
       <c r="E8" t="n">
-        <v>-7218.068523305154</v>
+        <v>-7218.068523305153</v>
       </c>
       <c r="F8" t="n">
-        <v>-1790.426177904028</v>
+        <v>-1790.426177904032</v>
       </c>
       <c r="G8" t="n">
-        <v>923.7065237641339</v>
+        <v>923.7065237641337</v>
       </c>
       <c r="H8" t="n">
         <v>3290.396906312708</v>
       </c>
       <c r="I8" t="n">
-        <v>655.4756848043041</v>
+        <v>655.4756848043044</v>
       </c>
     </row>
     <row r="9">
@@ -694,25 +694,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1859.913505855924</v>
+        <v>-1859.913505855927</v>
       </c>
       <c r="C9" t="n">
-        <v>137.4427839639936</v>
+        <v>137.4427839640016</v>
       </c>
       <c r="D9" t="n">
-        <v>5443.117187479218</v>
+        <v>5443.117187479216</v>
       </c>
       <c r="E9" t="n">
-        <v>-727.9858571020072</v>
+        <v>-727.9858571020084</v>
       </c>
       <c r="F9" t="n">
-        <v>-1869.841147277218</v>
+        <v>-1869.841147277217</v>
       </c>
       <c r="G9" t="n">
-        <v>84.40059098114405</v>
+        <v>84.40059098114423</v>
       </c>
       <c r="H9" t="n">
-        <v>655.475684804312</v>
+        <v>655.4756848043121</v>
       </c>
       <c r="I9" t="n">
         <v>196.1958253824856</v>
